--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-diagnose-prozedur-nein-unbekannt.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-diagnose-prozedur-nein-unbekannt.xlsx
@@ -892,7 +892,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-icd10gm|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-icd10gm|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Observation.code.coding:icd10-gm.id</t>
@@ -1021,7 +1021,7 @@
     <t>prozedurSnomed</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-sct|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-prozedur/ValueSet/procedures-sct|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Observation.code.coding:prozedurSnomed.id</t>
@@ -1060,7 +1060,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-alphaid|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-alphaid|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Observation.code.coding:alpha-id.id</t>
@@ -1111,7 +1111,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-orphanet|2026.0.1</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-diagnose/ValueSet/mii-vs-diagnose-orphanet|2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Observation.code.coding:orphanet.id</t>
